--- a/public/templates/forms/A-004-AssetCriticalityRankingMatrix-FORM.xlsx
+++ b/public/templates/forms/A-004-AssetCriticalityRankingMatrix-FORM.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="0"/>
   <fonts count="11">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -309,7 +309,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -343,7 +343,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/public/templates/forms/A-004-AssetCriticalityRankingMatrix-FORM.xlsx
+++ b/public/templates/forms/A-004-AssetCriticalityRankingMatrix-FORM.xlsx
@@ -4,20 +4,25 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Register!$20:$20</definedName>
+  </definedNames>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -135,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -188,6 +193,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -553,7 +561,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -745,7 +753,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="19.5" customHeight="1">
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Critical</t>
@@ -913,7 +921,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
+    <row r="21" ht="50.5" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>AST-001</t>
@@ -1103,7 +1111,6 @@
       </c>
       <c r="C33" s="13">
         <f>COUNTA(A21:A30)</f>
-        <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
@@ -1114,7 +1121,6 @@
       </c>
       <c r="C34" s="13">
         <f>COUNTIF(F21:F30,"Critical")</f>
-        <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
@@ -1125,7 +1131,6 @@
       </c>
       <c r="C35" s="13">
         <f>COUNTIF(F21:F30,"Important")</f>
-        <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
@@ -1136,7 +1141,6 @@
       </c>
       <c r="C36" s="13">
         <f>COUNTIF(F21:F30,"Supporting")</f>
-        <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1"/>
@@ -1213,7 +1217,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="19.5" customHeight="1">
+    <row r="48" ht="34.7" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
           <t>[Approving official / title]</t>
@@ -1263,7 +1267,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
+    <row r="53" ht="34.7" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
           <t>[#]</t>
@@ -1323,7 +1327,26 @@
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="A9:K9"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <dataValidations count="4">
+    <dataValidation sqref="A14:A16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Criticality Tier" prompt="Select a value" type="list">
+      <formula1>"Critical,Important,Supporting"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation sqref="D14:D16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Backup Priority" prompt="Select a value" type="list">
+      <formula1>"Highest,High,Routine"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation sqref="E14:E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Logging Scope" prompt="Select a value" type="list">
+      <formula1>"Baseline,Standard,Full / verbose"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation sqref="F14:F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Encryption Tier" prompt="Select a value" type="list">
+      <formula1>"Baseline,Standard,Strongest"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1331,7 +1354,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1356,7 +1379,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Scoring method, summary, downstream use, source authority, signatures and revision history live on the Register tab.</t>
@@ -1393,7 +1416,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Asset ID</t>
@@ -1591,7 +1614,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="34.7" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Owner (Role)</t>
@@ -1629,10 +1652,8 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
+      <c r="D17" s="20">
+        <v>46082</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1710,6 +1731,7 @@
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B24:D24"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>